--- a/site/public/downloads/ken/ken-basics.xlsx
+++ b/site/public/downloads/ken/ken-basics.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>台灣個人／家庭通膨每年 10% 起跳。官方 CPI 約 2% 左右，但房租、外食、醫療與照護的實際漲幅常遠高於 CPI；本工具採保守的 10% 起跳假設，讓規劃留足安全邊際。通膨格子設有驗證，低於 10% 會被拒絕，公式也以 MAX(10%, 輸入值) 計算。</t>
+          <t>台灣個人／家庭通膨每年 5% 起跳。官方 CPI 約 2% 左右，但房租、外食、醫療與照護的實際漲幅常遠高於 CPI；本工具採保守的 5% 起跳假設，讓規劃留足安全邊際。通膨格子設有驗證，低於 5% 會被拒絕，公式也以 MAX(5%, 輸入值) 計算。</t>
         </is>
       </c>
     </row>
@@ -970,15 +970,15 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B30" s="12">
-        <f>$B$27/(1+MAX(0.1,$B$29))^10</f>
+        <f>$B$27/(1+MAX(0.05,$B$29))^10</f>
         <v/>
       </c>
     </row>
@@ -1197,8 +1197,8 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1300,15 +1300,15 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B11" s="21">
-        <f>IFERROR(12*LN(1+$B$6*MAX(0.1,$B$10)/($B$4*12))/LN(1+MAX(0.1,$B$10)),0)</f>
+        <f>IFERROR(12*LN(1+$B$6*MAX(0.05,$B$10)/($B$4*12))/LN(1+MAX(0.05,$B$10)),0)</f>
         <v/>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C15" s="22">
-        <f>12*$B$4*((1+MAX(0.1,$B$10))^3-1)/MAX(0.1,$B$10)</f>
+        <f>12*$B$4*((1+MAX(0.05,$B$10))^3-1)/MAX(0.05,$B$10)</f>
         <v/>
       </c>
       <c r="D15" s="22">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="C16" s="22">
-        <f>12*$B$4*((1+MAX(0.1,$B$10))^$B$7-1)/MAX(0.1,$B$10)</f>
+        <f>12*$B$4*((1+MAX(0.05,$B$10))^$B$7-1)/MAX(0.05,$B$10)</f>
         <v/>
       </c>
       <c r="D16" s="22">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="C17" s="22">
-        <f>12*$B$4*1.2*((1+MAX(0.1,$B$10))^$B$7-1)/MAX(0.1,$B$10)</f>
+        <f>12*$B$4*1.2*((1+MAX(0.05,$B$10))^$B$7-1)/MAX(0.05,$B$10)</f>
         <v/>
       </c>
       <c r="D17" s="22">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C18" s="22">
-        <f>12*$B$5*((1+MAX(0.1,$B$10))^$B$7-1)/MAX(0.1,$B$10)</f>
+        <f>12*$B$5*((1+MAX(0.05,$B$10))^$B$7-1)/MAX(0.05,$B$10)</f>
         <v/>
       </c>
       <c r="D18" s="22">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="C19" s="22">
-        <f>12*$B$5*((1+MAX(0.1,$B$10))^$B$7-1)/MAX(0.1,$B$10)+$B$9*(1+MAX(0.1,$B$10))^$B$7</f>
+        <f>12*$B$5*((1+MAX(0.05,$B$10))^$B$7-1)/MAX(0.05,$B$10)+$B$9*(1+MAX(0.05,$B$10))^$B$7</f>
         <v/>
       </c>
       <c r="D19" s="22">
@@ -1520,8 +1520,8 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1583,15 +1583,15 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -1933,11 +1933,11 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>規劃採用通膨（實測與 10% 取高）</t>
+          <t>規劃採用通膨（實測與 5% 取高）</t>
         </is>
       </c>
       <c r="B24" s="27">
-        <f>MAX(MAX(0.1,$B$6),$B$23)</f>
+        <f>MAX(MAX(0.05,$B$6),$B$23)</f>
         <v/>
       </c>
     </row>
@@ -2066,8 +2066,8 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
     <dataValidation sqref="A8:A21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"食物雜貨,交通,生活必需,娛樂社交"</formula1>
@@ -2122,15 +2122,15 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="B31" s="12">
-        <f>$B$4*0.4*(1+MAX(0.1,$B$5))</f>
+        <f>$B$4*0.4*(1+MAX(0.05,$B$5))</f>
         <v/>
       </c>
     </row>
@@ -2588,8 +2588,8 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2650,15 +2650,15 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B27" s="12">
-        <f>$B$26/(1+MAX(0.1,$B$6))^$B$5</f>
+        <f>$B$26/(1+MAX(0.05,$B$6))^$B$5</f>
         <v/>
       </c>
     </row>
@@ -2928,8 +2928,8 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3000,15 +3000,15 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
         <v/>
       </c>
       <c r="C9" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^1</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^1</f>
         <v/>
       </c>
       <c r="D9" s="22">
@@ -3056,7 +3056,7 @@
         <v/>
       </c>
       <c r="E9" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^1</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^1</f>
         <v/>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
         <v/>
       </c>
       <c r="C10" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^2</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^2</f>
         <v/>
       </c>
       <c r="D10" s="22">
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="E10" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^2</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^2</f>
         <v/>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
         <v/>
       </c>
       <c r="C11" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^3</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^3</f>
         <v/>
       </c>
       <c r="D11" s="22">
@@ -3098,7 +3098,7 @@
         <v/>
       </c>
       <c r="E11" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^3</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^3</f>
         <v/>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="C12" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^4</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^4</f>
         <v/>
       </c>
       <c r="D12" s="22">
@@ -3119,7 +3119,7 @@
         <v/>
       </c>
       <c r="E12" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^4</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^4</f>
         <v/>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
         <v/>
       </c>
       <c r="C13" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^5</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^5</f>
         <v/>
       </c>
       <c r="D13" s="22">
@@ -3140,7 +3140,7 @@
         <v/>
       </c>
       <c r="E13" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^5</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^5</f>
         <v/>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
         <v/>
       </c>
       <c r="C14" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^6</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^6</f>
         <v/>
       </c>
       <c r="D14" s="22">
@@ -3161,7 +3161,7 @@
         <v/>
       </c>
       <c r="E14" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^6</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^6</f>
         <v/>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         <v/>
       </c>
       <c r="C15" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^7</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^7</f>
         <v/>
       </c>
       <c r="D15" s="22">
@@ -3182,7 +3182,7 @@
         <v/>
       </c>
       <c r="E15" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^7</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^7</f>
         <v/>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="C16" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^8</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^8</f>
         <v/>
       </c>
       <c r="D16" s="22">
@@ -3203,7 +3203,7 @@
         <v/>
       </c>
       <c r="E16" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^8</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^8</f>
         <v/>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
         <v/>
       </c>
       <c r="C17" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^9</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^9</f>
         <v/>
       </c>
       <c r="D17" s="22">
@@ -3224,7 +3224,7 @@
         <v/>
       </c>
       <c r="E17" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^9</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^9</f>
         <v/>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
         <v/>
       </c>
       <c r="C18" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^10</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^10</f>
         <v/>
       </c>
       <c r="D18" s="22">
@@ -3245,7 +3245,7 @@
         <v/>
       </c>
       <c r="E18" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^10</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^10</f>
         <v/>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
         <v/>
       </c>
       <c r="C19" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^11</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^11</f>
         <v/>
       </c>
       <c r="D19" s="22">
@@ -3266,7 +3266,7 @@
         <v/>
       </c>
       <c r="E19" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^11</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^11</f>
         <v/>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         <v/>
       </c>
       <c r="C20" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^12</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^12</f>
         <v/>
       </c>
       <c r="D20" s="22">
@@ -3287,7 +3287,7 @@
         <v/>
       </c>
       <c r="E20" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^12</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^12</f>
         <v/>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
         <v/>
       </c>
       <c r="C21" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^13</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^13</f>
         <v/>
       </c>
       <c r="D21" s="22">
@@ -3308,7 +3308,7 @@
         <v/>
       </c>
       <c r="E21" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^13</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^13</f>
         <v/>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
         <v/>
       </c>
       <c r="C22" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^14</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^14</f>
         <v/>
       </c>
       <c r="D22" s="22">
@@ -3329,7 +3329,7 @@
         <v/>
       </c>
       <c r="E22" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^14</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^14</f>
         <v/>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         <v/>
       </c>
       <c r="C23" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^15</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^15</f>
         <v/>
       </c>
       <c r="D23" s="22">
@@ -3350,7 +3350,7 @@
         <v/>
       </c>
       <c r="E23" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^15</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^15</f>
         <v/>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
         <v/>
       </c>
       <c r="C24" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^16</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^16</f>
         <v/>
       </c>
       <c r="D24" s="22">
@@ -3371,7 +3371,7 @@
         <v/>
       </c>
       <c r="E24" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^16</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^16</f>
         <v/>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
         <v/>
       </c>
       <c r="C25" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^17</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^17</f>
         <v/>
       </c>
       <c r="D25" s="22">
@@ -3392,7 +3392,7 @@
         <v/>
       </c>
       <c r="E25" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^17</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^17</f>
         <v/>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
         <v/>
       </c>
       <c r="C26" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^18</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^18</f>
         <v/>
       </c>
       <c r="D26" s="22">
@@ -3413,7 +3413,7 @@
         <v/>
       </c>
       <c r="E26" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^18</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^18</f>
         <v/>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
         <v/>
       </c>
       <c r="C27" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^19</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^19</f>
         <v/>
       </c>
       <c r="D27" s="22">
@@ -3434,7 +3434,7 @@
         <v/>
       </c>
       <c r="E27" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^19</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^19</f>
         <v/>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
         <v/>
       </c>
       <c r="C28" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^20</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^20</f>
         <v/>
       </c>
       <c r="D28" s="22">
@@ -3455,7 +3455,7 @@
         <v/>
       </c>
       <c r="E28" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^20</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^20</f>
         <v/>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
         <v/>
       </c>
       <c r="C29" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^21</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^21</f>
         <v/>
       </c>
       <c r="D29" s="22">
@@ -3476,7 +3476,7 @@
         <v/>
       </c>
       <c r="E29" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^21</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^21</f>
         <v/>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
         <v/>
       </c>
       <c r="C30" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^22</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^22</f>
         <v/>
       </c>
       <c r="D30" s="22">
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="E30" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^22</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^22</f>
         <v/>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
         <v/>
       </c>
       <c r="C31" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^23</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^23</f>
         <v/>
       </c>
       <c r="D31" s="22">
@@ -3518,7 +3518,7 @@
         <v/>
       </c>
       <c r="E31" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^23</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^23</f>
         <v/>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
         <v/>
       </c>
       <c r="C32" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^24</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^24</f>
         <v/>
       </c>
       <c r="D32" s="22">
@@ -3539,7 +3539,7 @@
         <v/>
       </c>
       <c r="E32" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^24</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^24</f>
         <v/>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
         <v/>
       </c>
       <c r="C33" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^25</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^25</f>
         <v/>
       </c>
       <c r="D33" s="22">
@@ -3560,7 +3560,7 @@
         <v/>
       </c>
       <c r="E33" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^25</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^25</f>
         <v/>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="C34" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^26</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^26</f>
         <v/>
       </c>
       <c r="D34" s="22">
@@ -3581,7 +3581,7 @@
         <v/>
       </c>
       <c r="E34" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^26</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^26</f>
         <v/>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
         <v/>
       </c>
       <c r="C35" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^27</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^27</f>
         <v/>
       </c>
       <c r="D35" s="22">
@@ -3602,7 +3602,7 @@
         <v/>
       </c>
       <c r="E35" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^27</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^27</f>
         <v/>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
         <v/>
       </c>
       <c r="C36" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^28</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^28</f>
         <v/>
       </c>
       <c r="D36" s="22">
@@ -3623,7 +3623,7 @@
         <v/>
       </c>
       <c r="E36" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^28</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^28</f>
         <v/>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
         <v/>
       </c>
       <c r="C37" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^29</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^29</f>
         <v/>
       </c>
       <c r="D37" s="22">
@@ -3644,7 +3644,7 @@
         <v/>
       </c>
       <c r="E37" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^29</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^29</f>
         <v/>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v/>
       </c>
       <c r="C38" s="22">
-        <f>$B$4*((1+$B$5)/(1+MAX(0.1,$B$7)))^30</f>
+        <f>$B$4*((1+$B$5)/(1+MAX(0.05,$B$7)))^30</f>
         <v/>
       </c>
       <c r="D38" s="22">
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="E38" s="22">
-        <f>$B$4*((1+$B$6)/(1+MAX(0.1,$B$7)))^30</f>
+        <f>$B$4*((1+$B$6)/(1+MAX(0.05,$B$7)))^30</f>
         <v/>
       </c>
     </row>
@@ -3674,8 +3674,8 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3717,15 +3717,15 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="B21" s="12">
-        <f>$B$17*(1+MAX(0.1,$B$4))^$B$19</f>
+        <f>$B$17*(1+MAX(0.05,$B$4))^$B$19</f>
         <v/>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
         <v>12</v>
       </c>
       <c r="D27" s="22">
-        <f>B27*(1+MAX(0.1,$B$4))^(C27/12)</f>
+        <f>B27*(1+MAX(0.05,$B$4))^(C27/12)</f>
         <v/>
       </c>
       <c r="E27" s="22">
@@ -4059,7 +4059,7 @@
         <v>12</v>
       </c>
       <c r="D28" s="22">
-        <f>B28*(1+MAX(0.1,$B$4))^(C28/12)</f>
+        <f>B28*(1+MAX(0.05,$B$4))^(C28/12)</f>
         <v/>
       </c>
       <c r="E28" s="22">
@@ -4072,7 +4072,7 @@
       <c r="B29" s="14" t="n"/>
       <c r="C29" s="14" t="n"/>
       <c r="D29" s="22">
-        <f>IF(C29&gt;0,B29*(1+MAX(0.1,$B$4))^(C29/12),"")</f>
+        <f>IF(C29&gt;0,B29*(1+MAX(0.05,$B$4))^(C29/12),"")</f>
         <v/>
       </c>
       <c r="E29" s="22">
@@ -4085,7 +4085,7 @@
       <c r="B30" s="14" t="n"/>
       <c r="C30" s="14" t="n"/>
       <c r="D30" s="22">
-        <f>IF(C30&gt;0,B30*(1+MAX(0.1,$B$4))^(C30/12),"")</f>
+        <f>IF(C30&gt;0,B30*(1+MAX(0.05,$B$4))^(C30/12),"")</f>
         <v/>
       </c>
       <c r="E30" s="22">
@@ -4098,7 +4098,7 @@
       <c r="B31" s="14" t="n"/>
       <c r="C31" s="14" t="n"/>
       <c r="D31" s="22">
-        <f>IF(C31&gt;0,B31*(1+MAX(0.1,$B$4))^(C31/12),"")</f>
+        <f>IF(C31&gt;0,B31*(1+MAX(0.05,$B$4))^(C31/12),"")</f>
         <v/>
       </c>
       <c r="E31" s="22">
@@ -4111,7 +4111,7 @@
       <c r="B32" s="14" t="n"/>
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="22">
-        <f>IF(C32&gt;0,B32*(1+MAX(0.1,$B$4))^(C32/12),"")</f>
+        <f>IF(C32&gt;0,B32*(1+MAX(0.05,$B$4))^(C32/12),"")</f>
         <v/>
       </c>
       <c r="E32" s="22">
@@ -4132,8 +4132,8 @@
     <mergeCell ref="A33:F33"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
